--- a/Experiment/Orders/PAR07_RUN03.xlsx
+++ b/Experiment/Orders/PAR07_RUN03.xlsx
@@ -27,315 +27,315 @@
     <t>3D_Face</t>
   </si>
   <si>
+    <t>3D_Object</t>
+  </si>
+  <si>
     <t>2D_Face</t>
   </si>
   <si>
     <t>3D_Hand</t>
   </si>
   <si>
+    <t>2D_Hand</t>
+  </si>
+  <si>
     <t>2D_Object</t>
   </si>
   <si>
-    <t>2D_Hand</t>
-  </si>
-  <si>
-    <t>3D_Object</t>
-  </si>
-  <si>
     <t>Duration_Seconds</t>
   </si>
   <si>
     <t>Filename_left</t>
   </si>
   <si>
+    <t>Face_15_L.png</t>
+  </si>
+  <si>
+    <t>Object_11_L.png</t>
+  </si>
+  <si>
+    <t>Face_03_R.png</t>
+  </si>
+  <si>
+    <t>Hand_12_L.png</t>
+  </si>
+  <si>
+    <t>Hand_01_R.png</t>
+  </si>
+  <si>
+    <t>Hand_03_L.png</t>
+  </si>
+  <si>
+    <t>Hand_07_L.png</t>
+  </si>
+  <si>
+    <t>Object_13_R.png</t>
+  </si>
+  <si>
+    <t>Hand_09_R.png</t>
+  </si>
+  <si>
+    <t>Face_10_L.png</t>
+  </si>
+  <si>
+    <t>Hand_01_L.png</t>
+  </si>
+  <si>
+    <t>Face_13_L.png</t>
+  </si>
+  <si>
+    <t>Face_07_L.png</t>
+  </si>
+  <si>
+    <t>Object_02_R.png</t>
+  </si>
+  <si>
+    <t>Face_05_L.png</t>
+  </si>
+  <si>
+    <t>Hand_12_R.png</t>
+  </si>
+  <si>
+    <t>Object_14_R.png</t>
+  </si>
+  <si>
+    <t>Hand_16_L.png</t>
+  </si>
+  <si>
+    <t>Object_10_L.png</t>
+  </si>
+  <si>
+    <t>Hand_02_R.png</t>
+  </si>
+  <si>
+    <t>Face_13_R.png</t>
+  </si>
+  <si>
+    <t>Face_01_R.png</t>
+  </si>
+  <si>
+    <t>Object_07_L.png</t>
+  </si>
+  <si>
+    <t>Object_16_R.png</t>
+  </si>
+  <si>
+    <t>Object_07_R.png</t>
+  </si>
+  <si>
+    <t>Face_06_R.png</t>
+  </si>
+  <si>
+    <t>Object_08_R.png</t>
+  </si>
+  <si>
+    <t>Object_13_L.png</t>
+  </si>
+  <si>
+    <t>Object_09_L.png</t>
+  </si>
+  <si>
+    <t>Face_16_L.png</t>
+  </si>
+  <si>
+    <t>Face_15_R.png</t>
+  </si>
+  <si>
+    <t>Hand_05_R.png</t>
+  </si>
+  <si>
+    <t>Object_01_L.png</t>
+  </si>
+  <si>
+    <t>Hand_02_L.png</t>
+  </si>
+  <si>
+    <t>Face_02_R.png</t>
+  </si>
+  <si>
+    <t>Face_03_L.png</t>
+  </si>
+  <si>
+    <t>Face_08_R.png</t>
+  </si>
+  <si>
+    <t>Hand_09_L.png</t>
+  </si>
+  <si>
+    <t>Face_01_L.png</t>
+  </si>
+  <si>
+    <t>Object_15_R.png</t>
+  </si>
+  <si>
+    <t>Face_09_L.png</t>
+  </si>
+  <si>
+    <t>Hand_08_R.png</t>
+  </si>
+  <si>
+    <t>Hand_04_R.png</t>
+  </si>
+  <si>
+    <t>Hand_16_R.png</t>
+  </si>
+  <si>
+    <t>Object_14_L.png</t>
+  </si>
+  <si>
+    <t>Object_03_L.png</t>
+  </si>
+  <si>
+    <t>Hand_13_R.png</t>
+  </si>
+  <si>
+    <t>Hand_08_L.png</t>
+  </si>
+  <si>
+    <t>Hand_06_R.png</t>
+  </si>
+  <si>
+    <t>Object_10_R.png</t>
+  </si>
+  <si>
+    <t>Object_15_L.png</t>
+  </si>
+  <si>
+    <t>Face_09_R.png</t>
+  </si>
+  <si>
+    <t>Object_02_L.png</t>
+  </si>
+  <si>
+    <t>Face_08_L.png</t>
+  </si>
+  <si>
+    <t>Object_05_L.png</t>
+  </si>
+  <si>
+    <t>Object_03_R.png</t>
+  </si>
+  <si>
+    <t>Hand_07_R.png</t>
+  </si>
+  <si>
     <t>Face_04_L.png</t>
   </si>
   <si>
+    <t>Hand_11_L.png</t>
+  </si>
+  <si>
+    <t>Hand_06_L.png</t>
+  </si>
+  <si>
+    <t>Object_05_R.png</t>
+  </si>
+  <si>
+    <t>Hand_04_L.png</t>
+  </si>
+  <si>
+    <t>Object_06_L.png</t>
+  </si>
+  <si>
+    <t>Hand_13_L.png</t>
+  </si>
+  <si>
+    <t>Face_05_R.png</t>
+  </si>
+  <si>
+    <t>Object_04_R.png</t>
+  </si>
+  <si>
+    <t>Object_06_R.png</t>
+  </si>
+  <si>
+    <t>Face_12_R.png</t>
+  </si>
+  <si>
+    <t>Face_12_L.png</t>
+  </si>
+  <si>
+    <t>Face_02_L.png</t>
+  </si>
+  <si>
+    <t>Object_12_R.png</t>
+  </si>
+  <si>
+    <t>Face_16_R.png</t>
+  </si>
+  <si>
+    <t>Face_07_R.png</t>
+  </si>
+  <si>
+    <t>Hand_14_R.png</t>
+  </si>
+  <si>
+    <t>Face_11_R.png</t>
+  </si>
+  <si>
+    <t>Object_12_L.png</t>
+  </si>
+  <si>
+    <t>Hand_03_R.png</t>
+  </si>
+  <si>
+    <t>Face_14_L.png</t>
+  </si>
+  <si>
+    <t>Hand_10_R.png</t>
+  </si>
+  <si>
+    <t>Hand_10_L.png</t>
+  </si>
+  <si>
+    <t>Object_08_L.png</t>
+  </si>
+  <si>
+    <t>Object_01_R.png</t>
+  </si>
+  <si>
+    <t>Face_11_L.png</t>
+  </si>
+  <si>
+    <t>Hand_14_L.png</t>
+  </si>
+  <si>
+    <t>Object_09_R.png</t>
+  </si>
+  <si>
+    <t>Object_16_L.png</t>
+  </si>
+  <si>
+    <t>Hand_05_L.png</t>
+  </si>
+  <si>
+    <t>Hand_15_R.png</t>
+  </si>
+  <si>
     <t>Face_04_R.png</t>
   </si>
   <si>
-    <t>Hand_09_L.png</t>
-  </si>
-  <si>
-    <t>Hand_04_L.png</t>
-  </si>
-  <si>
-    <t>Object_12_R.png</t>
-  </si>
-  <si>
-    <t>Object_08_R.png</t>
-  </si>
-  <si>
-    <t>Face_09_L.png</t>
-  </si>
-  <si>
-    <t>Face_03_L.png</t>
-  </si>
-  <si>
-    <t>Object_01_R.png</t>
-  </si>
-  <si>
-    <t>Hand_08_R.png</t>
+    <t>Face_06_L.png</t>
+  </si>
+  <si>
+    <t>Face_14_R.png</t>
+  </si>
+  <si>
+    <t>Hand_11_R.png</t>
   </si>
   <si>
     <t>Object_04_L.png</t>
   </si>
   <si>
-    <t>Face_14_R.png</t>
-  </si>
-  <si>
-    <t>Hand_09_R.png</t>
-  </si>
-  <si>
-    <t>Object_07_R.png</t>
-  </si>
-  <si>
-    <t>Object_02_L.png</t>
-  </si>
-  <si>
-    <t>Hand_01_L.png</t>
-  </si>
-  <si>
-    <t>Face_02_R.png</t>
-  </si>
-  <si>
-    <t>Object_06_R.png</t>
-  </si>
-  <si>
-    <t>Hand_02_L.png</t>
-  </si>
-  <si>
-    <t>Face_12_L.png</t>
-  </si>
-  <si>
-    <t>Hand_06_R.png</t>
-  </si>
-  <si>
-    <t>Face_06_L.png</t>
-  </si>
-  <si>
-    <t>Hand_14_L.png</t>
-  </si>
-  <si>
-    <t>Object_10_L.png</t>
-  </si>
-  <si>
-    <t>Face_15_L.png</t>
-  </si>
-  <si>
-    <t>Object_15_L.png</t>
-  </si>
-  <si>
-    <t>Hand_14_R.png</t>
-  </si>
-  <si>
     <t>Face_10_R.png</t>
   </si>
   <si>
-    <t>Object_07_L.png</t>
-  </si>
-  <si>
-    <t>Object_10_R.png</t>
-  </si>
-  <si>
-    <t>Face_09_R.png</t>
-  </si>
-  <si>
-    <t>Face_11_R.png</t>
-  </si>
-  <si>
-    <t>Face_02_L.png</t>
-  </si>
-  <si>
-    <t>Hand_08_L.png</t>
-  </si>
-  <si>
-    <t>Hand_02_R.png</t>
-  </si>
-  <si>
-    <t>Hand_13_R.png</t>
-  </si>
-  <si>
-    <t>Hand_10_L.png</t>
-  </si>
-  <si>
-    <t>Hand_03_L.png</t>
-  </si>
-  <si>
-    <t>Face_16_L.png</t>
-  </si>
-  <si>
-    <t>Object_09_R.png</t>
-  </si>
-  <si>
-    <t>Hand_04_R.png</t>
-  </si>
-  <si>
-    <t>Face_03_R.png</t>
-  </si>
-  <si>
-    <t>Face_16_R.png</t>
-  </si>
-  <si>
-    <t>Hand_16_L.png</t>
-  </si>
-  <si>
-    <t>Object_09_L.png</t>
-  </si>
-  <si>
-    <t>Object_16_L.png</t>
-  </si>
-  <si>
-    <t>Hand_01_R.png</t>
-  </si>
-  <si>
-    <t>Face_13_L.png</t>
-  </si>
-  <si>
-    <t>Hand_05_R.png</t>
-  </si>
-  <si>
-    <t>Object_12_L.png</t>
-  </si>
-  <si>
-    <t>Face_07_L.png</t>
-  </si>
-  <si>
-    <t>Face_05_R.png</t>
-  </si>
-  <si>
-    <t>Object_02_R.png</t>
-  </si>
-  <si>
-    <t>Face_08_R.png</t>
-  </si>
-  <si>
-    <t>Face_08_L.png</t>
-  </si>
-  <si>
-    <t>Face_11_L.png</t>
-  </si>
-  <si>
-    <t>Object_03_L.png</t>
-  </si>
-  <si>
-    <t>Hand_13_L.png</t>
-  </si>
-  <si>
-    <t>Face_15_R.png</t>
-  </si>
-  <si>
-    <t>Hand_15_R.png</t>
+    <t>Object_11_R.png</t>
   </si>
   <si>
     <t>Hand_15_L.png</t>
   </si>
   <si>
-    <t>Hand_11_R.png</t>
-  </si>
-  <si>
-    <t>Hand_10_R.png</t>
-  </si>
-  <si>
-    <t>Object_05_R.png</t>
-  </si>
-  <si>
-    <t>Face_01_L.png</t>
-  </si>
-  <si>
-    <t>Object_11_R.png</t>
-  </si>
-  <si>
-    <t>Object_06_L.png</t>
-  </si>
-  <si>
-    <t>Face_07_R.png</t>
-  </si>
-  <si>
-    <t>Object_08_L.png</t>
-  </si>
-  <si>
-    <t>Object_11_L.png</t>
-  </si>
-  <si>
-    <t>Object_03_R.png</t>
-  </si>
-  <si>
-    <t>Hand_05_L.png</t>
-  </si>
-  <si>
-    <t>Object_16_R.png</t>
-  </si>
-  <si>
-    <t>Object_15_R.png</t>
-  </si>
-  <si>
-    <t>Hand_11_L.png</t>
-  </si>
-  <si>
-    <t>Object_13_L.png</t>
-  </si>
-  <si>
-    <t>Hand_06_L.png</t>
-  </si>
-  <si>
-    <t>Object_14_R.png</t>
-  </si>
-  <si>
-    <t>Object_14_L.png</t>
-  </si>
-  <si>
-    <t>Face_13_R.png</t>
-  </si>
-  <si>
-    <t>Object_05_L.png</t>
-  </si>
-  <si>
-    <t>Hand_03_R.png</t>
-  </si>
-  <si>
-    <t>Object_04_R.png</t>
-  </si>
-  <si>
-    <t>Face_01_R.png</t>
-  </si>
-  <si>
-    <t>Hand_12_L.png</t>
-  </si>
-  <si>
-    <t>Face_06_R.png</t>
-  </si>
-  <si>
-    <t>Face_05_L.png</t>
-  </si>
-  <si>
-    <t>Face_12_R.png</t>
-  </si>
-  <si>
-    <t>Object_13_R.png</t>
-  </si>
-  <si>
-    <t>Hand_12_R.png</t>
-  </si>
-  <si>
-    <t>Face_10_L.png</t>
-  </si>
-  <si>
-    <t>Hand_07_R.png</t>
-  </si>
-  <si>
-    <t>Object_01_L.png</t>
-  </si>
-  <si>
-    <t>Face_14_L.png</t>
-  </si>
-  <si>
-    <t>Hand_07_L.png</t>
-  </si>
-  <si>
-    <t>Hand_16_R.png</t>
-  </si>
-  <si>
     <t>Filename_right</t>
   </si>
   <si>
@@ -372,64 +372,64 @@
     <t>Face</t>
   </si>
   <si>
+    <t>Object</t>
+  </si>
+  <si>
     <t>Hand</t>
   </si>
   <si>
-    <t>Object</t>
-  </si>
-  <si>
     <t>Stim</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
     <t>04</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>05</t>
   </si>
 </sst>
 </file>
@@ -572,7 +572,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="F3" s="0" t="s">
         <v>109</v>
@@ -602,7 +602,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D4" s="0"/>
       <c r="E4" s="0"/>
@@ -636,7 +636,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="F5" s="0" t="s">
         <v>109</v>
@@ -649,13 +649,13 @@
         <v>113</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D6" s="0"/>
       <c r="E6" s="0"/>
@@ -700,7 +700,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F7" s="0" t="s">
         <v>109</v>
@@ -713,13 +713,13 @@
         <v>113</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
@@ -755,7 +755,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="0">
         <v>1</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="F9" s="0" t="s">
         <v>109</v>
@@ -780,10 +780,10 @@
         <v>115</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -819,7 +819,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="0">
         <v>1</v>
@@ -847,7 +847,7 @@
         <v>120</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -889,23 +889,23 @@
         <v>1</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G13" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="0"/>
       <c r="I13" s="0" t="s">
         <v>113</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K13" s="0" t="s">
         <v>120</v>
@@ -953,10 +953,10 @@
         <v>1</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>109</v>
@@ -969,13 +969,13 @@
         <v>113</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K15" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
@@ -1011,16 +1011,16 @@
         <v>8</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C17" s="0">
         <v>1</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>109</v>
@@ -1033,13 +1033,13 @@
         <v>113</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -1075,16 +1075,16 @@
         <v>9</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C19" s="0">
         <v>1</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="F19" s="0" t="s">
         <v>109</v>
@@ -1097,13 +1097,13 @@
         <v>113</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20">
@@ -1114,7 +1114,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D20" s="0"/>
       <c r="E20" s="0"/>
@@ -1139,16 +1139,16 @@
         <v>10</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C21" s="0">
         <v>1</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>109</v>
@@ -1161,13 +1161,13 @@
         <v>113</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22">
@@ -1203,16 +1203,16 @@
         <v>11</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="0">
         <v>1</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>109</v>
@@ -1225,13 +1225,13 @@
         <v>113</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24">
@@ -1242,7 +1242,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D24" s="0"/>
       <c r="E24" s="0"/>
@@ -1267,16 +1267,16 @@
         <v>12</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C25" s="0">
         <v>1</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>109</v>
@@ -1292,10 +1292,10 @@
         <v>115</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26">
@@ -1331,16 +1331,16 @@
         <v>13</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27" s="0">
         <v>1</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="F27" s="0" t="s">
         <v>109</v>
@@ -1353,13 +1353,13 @@
         <v>113</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K27" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28">
@@ -1395,16 +1395,16 @@
         <v>14</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" s="0">
         <v>1</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F29" s="0" t="s">
         <v>109</v>
@@ -1423,7 +1423,7 @@
         <v>119</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30">
@@ -1434,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D30" s="0"/>
       <c r="E30" s="0"/>
@@ -1459,16 +1459,16 @@
         <v>15</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C31" s="0">
         <v>1</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="F31" s="0" t="s">
         <v>109</v>
@@ -1481,13 +1481,13 @@
         <v>113</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32">
@@ -1523,16 +1523,16 @@
         <v>16</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" s="0">
         <v>1</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="F33" s="0" t="s">
         <v>109</v>
@@ -1545,13 +1545,13 @@
         <v>113</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K33" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34">
@@ -1587,16 +1587,16 @@
         <v>17</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C35" s="0">
         <v>1</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="F35" s="0" t="s">
         <v>109</v>
@@ -1609,13 +1609,13 @@
         <v>113</v>
       </c>
       <c r="J35" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K35" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36">
@@ -1651,16 +1651,16 @@
         <v>18</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C37" s="0">
         <v>1</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>109</v>
@@ -1673,13 +1673,13 @@
         <v>113</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38">
@@ -1690,7 +1690,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D38" s="0"/>
       <c r="E38" s="0"/>
@@ -1715,16 +1715,16 @@
         <v>19</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C39" s="0">
         <v>1</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F39" s="0" t="s">
         <v>109</v>
@@ -1737,13 +1737,13 @@
         <v>113</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40">
@@ -1779,16 +1779,16 @@
         <v>20</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C41" s="0">
         <v>1</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F41" s="0" t="s">
         <v>109</v>
@@ -1801,13 +1801,13 @@
         <v>113</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42">
@@ -1843,16 +1843,16 @@
         <v>21</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C43" s="0">
         <v>1</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="F43" s="0" t="s">
         <v>109</v>
@@ -1865,13 +1865,13 @@
         <v>113</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K43" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44">
@@ -1907,16 +1907,16 @@
         <v>22</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C45" s="0">
         <v>1</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F45" s="0" t="s">
         <v>109</v>
@@ -1932,10 +1932,10 @@
         <v>116</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46">
@@ -1971,16 +1971,16 @@
         <v>23</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C47" s="0">
         <v>1</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="F47" s="0" t="s">
         <v>109</v>
@@ -1996,10 +1996,10 @@
         <v>115</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48">
@@ -2035,16 +2035,16 @@
         <v>24</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C49" s="0">
         <v>1</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>109</v>
@@ -2057,13 +2057,13 @@
         <v>113</v>
       </c>
       <c r="J49" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K49" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50">
@@ -2105,10 +2105,10 @@
         <v>1</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F51" s="0" t="s">
         <v>109</v>
@@ -2121,13 +2121,13 @@
         <v>113</v>
       </c>
       <c r="J51" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K51" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52">
@@ -2138,7 +2138,7 @@
         <v>2</v>
       </c>
       <c r="C52" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D52" s="0"/>
       <c r="E52" s="0"/>
@@ -2163,7 +2163,7 @@
         <v>26</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C53" s="0">
         <v>1</v>
@@ -2172,26 +2172,26 @@
         <v>35</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="F53" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G53" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="0"/>
       <c r="I53" s="0" t="s">
         <v>113</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K53" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54">
@@ -2227,7 +2227,7 @@
         <v>27</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C55" s="0">
         <v>1</v>
@@ -2236,7 +2236,7 @@
         <v>36</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="F55" s="0" t="s">
         <v>109</v>
@@ -2249,13 +2249,13 @@
         <v>113</v>
       </c>
       <c r="J55" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56">
@@ -2266,7 +2266,7 @@
         <v>2</v>
       </c>
       <c r="C56" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D56" s="0"/>
       <c r="E56" s="0"/>
@@ -2291,7 +2291,7 @@
         <v>28</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C57" s="0">
         <v>1</v>
@@ -2319,7 +2319,7 @@
         <v>119</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58">
@@ -2330,7 +2330,7 @@
         <v>2</v>
       </c>
       <c r="C58" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D58" s="0"/>
       <c r="E58" s="0"/>
@@ -2364,7 +2364,7 @@
         <v>38</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F59" s="0" t="s">
         <v>109</v>
@@ -2377,13 +2377,13 @@
         <v>113</v>
       </c>
       <c r="J59" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60">
@@ -2394,7 +2394,7 @@
         <v>2</v>
       </c>
       <c r="C60" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D60" s="0"/>
       <c r="E60" s="0"/>
@@ -2419,7 +2419,7 @@
         <v>30</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C61" s="0">
         <v>1</v>
@@ -2428,7 +2428,7 @@
         <v>39</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="F61" s="0" t="s">
         <v>109</v>
@@ -2444,7 +2444,7 @@
         <v>115</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L61" s="0" t="s">
         <v>130</v>
@@ -2458,7 +2458,7 @@
         <v>2</v>
       </c>
       <c r="C62" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D62" s="0"/>
       <c r="E62" s="0"/>
@@ -2483,7 +2483,7 @@
         <v>31</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C63" s="0">
         <v>1</v>
@@ -2492,7 +2492,7 @@
         <v>40</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="F63" s="0" t="s">
         <v>109</v>
@@ -2505,13 +2505,13 @@
         <v>113</v>
       </c>
       <c r="J63" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64">
@@ -2547,7 +2547,7 @@
         <v>32</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C65" s="0">
         <v>1</v>
@@ -2575,7 +2575,7 @@
         <v>118</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66">
@@ -2611,7 +2611,7 @@
         <v>33</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C67" s="0">
         <v>1</v>
@@ -2636,10 +2636,10 @@
         <v>116</v>
       </c>
       <c r="K67" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="68">
@@ -2675,7 +2675,7 @@
         <v>34</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C69" s="0">
         <v>1</v>
@@ -2684,7 +2684,7 @@
         <v>43</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F69" s="0" t="s">
         <v>109</v>
@@ -2700,10 +2700,10 @@
         <v>115</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70">
@@ -2714,7 +2714,7 @@
         <v>2</v>
       </c>
       <c r="C70" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D70" s="0"/>
       <c r="E70" s="0"/>
@@ -2739,7 +2739,7 @@
         <v>35</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C71" s="0">
         <v>1</v>
@@ -2748,7 +2748,7 @@
         <v>44</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F71" s="0" t="s">
         <v>109</v>
@@ -2764,10 +2764,10 @@
         <v>115</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="72">
@@ -2778,7 +2778,7 @@
         <v>2</v>
       </c>
       <c r="C72" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D72" s="0"/>
       <c r="E72" s="0"/>
@@ -2803,7 +2803,7 @@
         <v>36</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C73" s="0">
         <v>1</v>
@@ -2828,10 +2828,10 @@
         <v>116</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74">
@@ -2867,7 +2867,7 @@
         <v>37</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C75" s="0">
         <v>1</v>
@@ -2876,7 +2876,7 @@
         <v>46</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="F75" s="0" t="s">
         <v>109</v>
@@ -2889,13 +2889,13 @@
         <v>113</v>
       </c>
       <c r="J75" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76">
@@ -2940,7 +2940,7 @@
         <v>47</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="F77" s="0" t="s">
         <v>109</v>
@@ -2953,13 +2953,13 @@
         <v>113</v>
       </c>
       <c r="J77" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K77" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="78">
@@ -2995,7 +2995,7 @@
         <v>39</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C79" s="0">
         <v>1</v>
@@ -3004,7 +3004,7 @@
         <v>48</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="F79" s="0" t="s">
         <v>109</v>
@@ -3020,10 +3020,10 @@
         <v>115</v>
       </c>
       <c r="K79" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="80">
@@ -3068,7 +3068,7 @@
         <v>49</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F81" s="0" t="s">
         <v>109</v>
@@ -3087,7 +3087,7 @@
         <v>118</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="82">
@@ -3098,7 +3098,7 @@
         <v>2</v>
       </c>
       <c r="C82" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D82" s="0"/>
       <c r="E82" s="0"/>
@@ -3123,7 +3123,7 @@
         <v>41</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C83" s="0">
         <v>1</v>
@@ -3148,10 +3148,10 @@
         <v>116</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="84">
@@ -3162,7 +3162,7 @@
         <v>2</v>
       </c>
       <c r="C84" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D84" s="0"/>
       <c r="E84" s="0"/>
@@ -3187,7 +3187,7 @@
         <v>42</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C85" s="0">
         <v>1</v>
@@ -3196,7 +3196,7 @@
         <v>51</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F85" s="0" t="s">
         <v>109</v>
@@ -3209,13 +3209,13 @@
         <v>113</v>
       </c>
       <c r="J85" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K85" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="86">
@@ -3226,7 +3226,7 @@
         <v>2</v>
       </c>
       <c r="C86" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D86" s="0"/>
       <c r="E86" s="0"/>
@@ -3251,7 +3251,7 @@
         <v>43</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C87" s="0">
         <v>1</v>
@@ -3276,10 +3276,10 @@
         <v>116</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88">
@@ -3290,7 +3290,7 @@
         <v>2</v>
       </c>
       <c r="C88" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D88" s="0"/>
       <c r="E88" s="0"/>
@@ -3315,7 +3315,7 @@
         <v>44</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C89" s="0">
         <v>1</v>
@@ -3340,10 +3340,10 @@
         <v>116</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="90">
@@ -3354,7 +3354,7 @@
         <v>2</v>
       </c>
       <c r="C90" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D90" s="0"/>
       <c r="E90" s="0"/>
@@ -3379,7 +3379,7 @@
         <v>45</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C91" s="0">
         <v>1</v>
@@ -3388,7 +3388,7 @@
         <v>54</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="F91" s="0" t="s">
         <v>109</v>
@@ -3401,13 +3401,13 @@
         <v>113</v>
       </c>
       <c r="J91" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K91" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="92">
@@ -3418,7 +3418,7 @@
         <v>2</v>
       </c>
       <c r="C92" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D92" s="0"/>
       <c r="E92" s="0"/>
@@ -3443,7 +3443,7 @@
         <v>46</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C93" s="0">
         <v>1</v>
@@ -3452,7 +3452,7 @@
         <v>55</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F93" s="0" t="s">
         <v>109</v>
@@ -3468,10 +3468,10 @@
         <v>115</v>
       </c>
       <c r="K93" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="94">
@@ -3507,7 +3507,7 @@
         <v>47</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C95" s="0">
         <v>1</v>
@@ -3516,7 +3516,7 @@
         <v>56</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="F95" s="0" t="s">
         <v>109</v>
@@ -3532,10 +3532,10 @@
         <v>115</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="96">
@@ -3596,10 +3596,10 @@
         <v>116</v>
       </c>
       <c r="K97" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="98">
@@ -3635,7 +3635,7 @@
         <v>49</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C99" s="0">
         <v>1</v>
@@ -3644,7 +3644,7 @@
         <v>58</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="F99" s="0" t="s">
         <v>109</v>
@@ -3660,10 +3660,10 @@
         <v>115</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="100">
@@ -3674,7 +3674,7 @@
         <v>2</v>
       </c>
       <c r="C100" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D100" s="0"/>
       <c r="E100" s="0"/>
@@ -3724,10 +3724,10 @@
         <v>116</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="102">
@@ -3772,7 +3772,7 @@
         <v>60</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F103" s="0" t="s">
         <v>109</v>
@@ -3785,13 +3785,13 @@
         <v>113</v>
       </c>
       <c r="J103" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="104">
@@ -3827,7 +3827,7 @@
         <v>52</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C105" s="0">
         <v>1</v>
@@ -3836,7 +3836,7 @@
         <v>61</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="F105" s="0" t="s">
         <v>109</v>
@@ -3852,10 +3852,10 @@
         <v>115</v>
       </c>
       <c r="K105" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L105" s="0" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="106">
@@ -3891,7 +3891,7 @@
         <v>53</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C107" s="0">
         <v>1</v>
@@ -3919,7 +3919,7 @@
         <v>118</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="108">
@@ -3930,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="C108" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D108" s="0"/>
       <c r="E108" s="0"/>
@@ -3955,7 +3955,7 @@
         <v>54</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C109" s="0">
         <v>1</v>
@@ -3964,7 +3964,7 @@
         <v>63</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="F109" s="0" t="s">
         <v>109</v>
@@ -3977,13 +3977,13 @@
         <v>113</v>
       </c>
       <c r="J109" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="110">
@@ -4019,7 +4019,7 @@
         <v>55</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C111" s="0">
         <v>1</v>
@@ -4028,7 +4028,7 @@
         <v>64</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="F111" s="0" t="s">
         <v>109</v>
@@ -4041,13 +4041,13 @@
         <v>113</v>
       </c>
       <c r="J111" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K111" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="112">
@@ -4058,7 +4058,7 @@
         <v>2</v>
       </c>
       <c r="C112" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D112" s="0"/>
       <c r="E112" s="0"/>
@@ -4083,7 +4083,7 @@
         <v>56</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C113" s="0">
         <v>1</v>
@@ -4092,7 +4092,7 @@
         <v>65</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F113" s="0" t="s">
         <v>109</v>
@@ -4108,10 +4108,10 @@
         <v>115</v>
       </c>
       <c r="K113" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="114">
@@ -4122,7 +4122,7 @@
         <v>2</v>
       </c>
       <c r="C114" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D114" s="0"/>
       <c r="E114" s="0"/>
@@ -4147,7 +4147,7 @@
         <v>57</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C115" s="0">
         <v>1</v>
@@ -4156,7 +4156,7 @@
         <v>66</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F115" s="0" t="s">
         <v>109</v>
@@ -4169,13 +4169,13 @@
         <v>113</v>
       </c>
       <c r="J115" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K115" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="116">
@@ -4211,7 +4211,7 @@
         <v>58</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C117" s="0">
         <v>1</v>
@@ -4220,7 +4220,7 @@
         <v>67</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F117" s="0" t="s">
         <v>109</v>
@@ -4233,13 +4233,13 @@
         <v>113</v>
       </c>
       <c r="J117" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K117" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="118">
@@ -4250,7 +4250,7 @@
         <v>2</v>
       </c>
       <c r="C118" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D118" s="0"/>
       <c r="E118" s="0"/>
@@ -4275,7 +4275,7 @@
         <v>59</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C119" s="0">
         <v>1</v>
@@ -4284,7 +4284,7 @@
         <v>68</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="F119" s="0" t="s">
         <v>109</v>
@@ -4300,10 +4300,10 @@
         <v>115</v>
       </c>
       <c r="K119" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="120">
@@ -4314,7 +4314,7 @@
         <v>2</v>
       </c>
       <c r="C120" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D120" s="0"/>
       <c r="E120" s="0"/>
@@ -4339,7 +4339,7 @@
         <v>60</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C121" s="0">
         <v>1</v>
@@ -4348,7 +4348,7 @@
         <v>69</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="F121" s="0" t="s">
         <v>109</v>
@@ -4361,13 +4361,13 @@
         <v>113</v>
       </c>
       <c r="J121" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L121" s="0" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
     </row>
     <row r="122">
@@ -4403,7 +4403,7 @@
         <v>61</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C123" s="0">
         <v>1</v>
@@ -4412,7 +4412,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F123" s="0" t="s">
         <v>109</v>
@@ -4425,13 +4425,13 @@
         <v>113</v>
       </c>
       <c r="J123" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K123" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="124">
@@ -4442,7 +4442,7 @@
         <v>2</v>
       </c>
       <c r="C124" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D124" s="0"/>
       <c r="E124" s="0"/>
@@ -4467,7 +4467,7 @@
         <v>62</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C125" s="0">
         <v>1</v>
@@ -4476,7 +4476,7 @@
         <v>71</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F125" s="0" t="s">
         <v>109</v>
@@ -4489,13 +4489,13 @@
         <v>113</v>
       </c>
       <c r="J125" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K125" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="126">
@@ -4506,7 +4506,7 @@
         <v>2</v>
       </c>
       <c r="C126" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D126" s="0"/>
       <c r="E126" s="0"/>
@@ -4531,7 +4531,7 @@
         <v>63</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C127" s="0">
         <v>1</v>
@@ -4540,7 +4540,7 @@
         <v>72</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F127" s="0" t="s">
         <v>109</v>
@@ -4553,13 +4553,13 @@
         <v>113</v>
       </c>
       <c r="J127" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K127" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="128">
@@ -4570,7 +4570,7 @@
         <v>2</v>
       </c>
       <c r="C128" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D128" s="0"/>
       <c r="E128" s="0"/>
@@ -4595,7 +4595,7 @@
         <v>64</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C129" s="0">
         <v>1</v>
@@ -4604,7 +4604,7 @@
         <v>73</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F129" s="0" t="s">
         <v>109</v>
@@ -4617,13 +4617,13 @@
         <v>113</v>
       </c>
       <c r="J129" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K129" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="130">
@@ -4668,7 +4668,7 @@
         <v>74</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F131" s="0" t="s">
         <v>109</v>
@@ -4681,13 +4681,13 @@
         <v>113</v>
       </c>
       <c r="J131" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K131" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="132">
@@ -4723,7 +4723,7 @@
         <v>66</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C133" s="0">
         <v>1</v>
@@ -4732,7 +4732,7 @@
         <v>75</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="F133" s="0" t="s">
         <v>109</v>
@@ -4745,13 +4745,13 @@
         <v>113</v>
       </c>
       <c r="J133" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K133" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="134">
@@ -4787,7 +4787,7 @@
         <v>67</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C135" s="0">
         <v>1</v>
@@ -4812,10 +4812,10 @@
         <v>116</v>
       </c>
       <c r="K135" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="136">
@@ -4860,7 +4860,7 @@
         <v>77</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="F137" s="0" t="s">
         <v>109</v>
@@ -4873,13 +4873,13 @@
         <v>113</v>
       </c>
       <c r="J137" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="138">
@@ -4915,7 +4915,7 @@
         <v>69</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C139" s="0">
         <v>1</v>
@@ -4943,7 +4943,7 @@
         <v>118</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="140">
@@ -4954,7 +4954,7 @@
         <v>2</v>
       </c>
       <c r="C140" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D140" s="0"/>
       <c r="E140" s="0"/>
@@ -4979,7 +4979,7 @@
         <v>70</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C141" s="0">
         <v>1</v>
@@ -4988,7 +4988,7 @@
         <v>79</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="F141" s="0" t="s">
         <v>109</v>
@@ -5004,7 +5004,7 @@
         <v>115</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L141" s="0" t="s">
         <v>126</v>
@@ -5018,7 +5018,7 @@
         <v>2</v>
       </c>
       <c r="C142" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D142" s="0"/>
       <c r="E142" s="0"/>
@@ -5043,7 +5043,7 @@
         <v>71</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C143" s="0">
         <v>1</v>
@@ -5052,7 +5052,7 @@
         <v>80</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="F143" s="0" t="s">
         <v>109</v>
@@ -5068,10 +5068,10 @@
         <v>115</v>
       </c>
       <c r="K143" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L143" s="0" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="144">
@@ -5082,7 +5082,7 @@
         <v>2</v>
       </c>
       <c r="C144" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D144" s="0"/>
       <c r="E144" s="0"/>
@@ -5107,7 +5107,7 @@
         <v>72</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C145" s="0">
         <v>1</v>
@@ -5132,10 +5132,10 @@
         <v>116</v>
       </c>
       <c r="K145" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L145" s="0" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="146">
@@ -5180,7 +5180,7 @@
         <v>82</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="F147" s="0" t="s">
         <v>109</v>
@@ -5193,13 +5193,13 @@
         <v>113</v>
       </c>
       <c r="J147" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K147" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L147" s="0" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="148">
@@ -5235,7 +5235,7 @@
         <v>74</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C149" s="0">
         <v>1</v>
@@ -5260,10 +5260,10 @@
         <v>116</v>
       </c>
       <c r="K149" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L149" s="0" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="150">
@@ -5299,7 +5299,7 @@
         <v>75</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C151" s="0">
         <v>1</v>
@@ -5363,35 +5363,35 @@
         <v>76</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C153" s="0">
         <v>1</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F153" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G153" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153" s="0"/>
       <c r="I153" s="0" t="s">
         <v>113</v>
       </c>
       <c r="J153" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K153" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L153" s="0" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="154">
@@ -5427,16 +5427,16 @@
         <v>77</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C155" s="0">
         <v>1</v>
       </c>
       <c r="D155" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="F155" s="0" t="s">
         <v>109</v>
@@ -5449,13 +5449,13 @@
         <v>113</v>
       </c>
       <c r="J155" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K155" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L155" s="0" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="156">
@@ -5466,7 +5466,7 @@
         <v>2</v>
       </c>
       <c r="C156" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D156" s="0"/>
       <c r="E156" s="0"/>
@@ -5491,16 +5491,16 @@
         <v>78</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C157" s="0">
         <v>1</v>
       </c>
       <c r="D157" s="0" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="F157" s="0" t="s">
         <v>109</v>
@@ -5519,7 +5519,7 @@
         <v>119</v>
       </c>
       <c r="L157" s="0" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="158">
@@ -5555,16 +5555,16 @@
         <v>79</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C159" s="0">
         <v>1</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E159" s="0" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F159" s="0" t="s">
         <v>109</v>
@@ -5583,7 +5583,7 @@
         <v>120</v>
       </c>
       <c r="L159" s="0" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="160">
@@ -5619,16 +5619,16 @@
         <v>80</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C161" s="0">
         <v>1</v>
       </c>
       <c r="D161" s="0" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E161" s="0" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F161" s="0" t="s">
         <v>109</v>
@@ -5644,10 +5644,10 @@
         <v>115</v>
       </c>
       <c r="K161" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L161" s="0" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="162">
@@ -5658,7 +5658,7 @@
         <v>2</v>
       </c>
       <c r="C162" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D162" s="0"/>
       <c r="E162" s="0"/>
@@ -5683,16 +5683,16 @@
         <v>81</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C163" s="0">
         <v>1</v>
       </c>
       <c r="D163" s="0" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E163" s="0" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F163" s="0" t="s">
         <v>109</v>
@@ -5708,10 +5708,10 @@
         <v>116</v>
       </c>
       <c r="K163" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L163" s="0" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="164">
@@ -5747,16 +5747,16 @@
         <v>82</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C165" s="0">
         <v>1</v>
       </c>
       <c r="D165" s="0" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F165" s="0" t="s">
         <v>109</v>
@@ -5775,7 +5775,7 @@
         <v>120</v>
       </c>
       <c r="L165" s="0" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="166">
@@ -5811,16 +5811,16 @@
         <v>83</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C167" s="0">
         <v>1</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="F167" s="0" t="s">
         <v>109</v>
@@ -5833,13 +5833,13 @@
         <v>113</v>
       </c>
       <c r="J167" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K167" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L167" s="0" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="168">
@@ -5875,16 +5875,16 @@
         <v>84</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C169" s="0">
         <v>1</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E169" s="0" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F169" s="0" t="s">
         <v>109</v>
@@ -5900,10 +5900,10 @@
         <v>116</v>
       </c>
       <c r="K169" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L169" s="0" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="170">
@@ -5914,7 +5914,7 @@
         <v>2</v>
       </c>
       <c r="C170" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D170" s="0"/>
       <c r="E170" s="0"/>
@@ -5939,16 +5939,16 @@
         <v>85</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C171" s="0">
         <v>1</v>
       </c>
       <c r="D171" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="F171" s="0" t="s">
         <v>109</v>
@@ -5961,13 +5961,13 @@
         <v>113</v>
       </c>
       <c r="J171" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K171" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L171" s="0" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="172">
@@ -5978,7 +5978,7 @@
         <v>2</v>
       </c>
       <c r="C172" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D172" s="0"/>
       <c r="E172" s="0"/>
@@ -6003,16 +6003,16 @@
         <v>86</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C173" s="0">
         <v>1</v>
       </c>
       <c r="D173" s="0" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F173" s="0" t="s">
         <v>109</v>
@@ -6028,10 +6028,10 @@
         <v>115</v>
       </c>
       <c r="K173" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L173" s="0" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="174">
@@ -6067,16 +6067,16 @@
         <v>87</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C175" s="0">
         <v>1</v>
       </c>
       <c r="D175" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F175" s="0" t="s">
         <v>109</v>
@@ -6092,10 +6092,10 @@
         <v>116</v>
       </c>
       <c r="K175" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L175" s="0" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="176">
@@ -6106,7 +6106,7 @@
         <v>2</v>
       </c>
       <c r="C176" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D176" s="0"/>
       <c r="E176" s="0"/>
@@ -6131,16 +6131,16 @@
         <v>88</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C177" s="0">
         <v>1</v>
       </c>
       <c r="D177" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E177" s="0" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="F177" s="0" t="s">
         <v>109</v>
@@ -6156,10 +6156,10 @@
         <v>115</v>
       </c>
       <c r="K177" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L177" s="0" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="178">
@@ -6170,7 +6170,7 @@
         <v>2</v>
       </c>
       <c r="C178" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D178" s="0"/>
       <c r="E178" s="0"/>
@@ -6195,16 +6195,16 @@
         <v>89</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C179" s="0">
         <v>1</v>
       </c>
       <c r="D179" s="0" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="F179" s="0" t="s">
         <v>109</v>
@@ -6217,13 +6217,13 @@
         <v>113</v>
       </c>
       <c r="J179" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K179" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L179" s="0" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="180">
@@ -6259,16 +6259,16 @@
         <v>90</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C181" s="0">
         <v>1</v>
       </c>
       <c r="D181" s="0" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F181" s="0" t="s">
         <v>109</v>
@@ -6287,7 +6287,7 @@
         <v>120</v>
       </c>
       <c r="L181" s="0" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="182">
@@ -6298,7 +6298,7 @@
         <v>2</v>
       </c>
       <c r="C182" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D182" s="0"/>
       <c r="E182" s="0"/>
@@ -6323,16 +6323,16 @@
         <v>91</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C183" s="0">
         <v>1</v>
       </c>
       <c r="D183" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F183" s="0" t="s">
         <v>109</v>
@@ -6348,10 +6348,10 @@
         <v>116</v>
       </c>
       <c r="K183" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L183" s="0" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="184">
@@ -6393,10 +6393,10 @@
         <v>1</v>
       </c>
       <c r="D185" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F185" s="0" t="s">
         <v>109</v>
@@ -6415,7 +6415,7 @@
         <v>118</v>
       </c>
       <c r="L185" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="186">
@@ -6451,16 +6451,16 @@
         <v>93</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C187" s="0">
         <v>1</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F187" s="0" t="s">
         <v>109</v>
@@ -6476,10 +6476,10 @@
         <v>116</v>
       </c>
       <c r="K187" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L187" s="0" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="188">
@@ -6490,7 +6490,7 @@
         <v>2</v>
       </c>
       <c r="C188" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D188" s="0"/>
       <c r="E188" s="0"/>
@@ -6515,16 +6515,16 @@
         <v>94</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C189" s="0">
         <v>1</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="F189" s="0" t="s">
         <v>109</v>
@@ -6537,13 +6537,13 @@
         <v>113</v>
       </c>
       <c r="J189" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K189" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L189" s="0" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="190">
@@ -6579,7 +6579,7 @@
         <v>95</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C191" s="0">
         <v>1</v>
@@ -6588,13 +6588,13 @@
         <v>103</v>
       </c>
       <c r="E191" s="0" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="F191" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G191" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H191" s="0"/>
       <c r="I191" s="0" t="s">
@@ -6604,10 +6604,10 @@
         <v>115</v>
       </c>
       <c r="K191" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L191" s="0" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="192">
@@ -6618,7 +6618,7 @@
         <v>2</v>
       </c>
       <c r="C192" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D192" s="0"/>
       <c r="E192" s="0"/>
@@ -6643,7 +6643,7 @@
         <v>96</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C193" s="0">
         <v>1</v>
@@ -6652,7 +6652,7 @@
         <v>104</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="F193" s="0" t="s">
         <v>109</v>
@@ -6665,13 +6665,13 @@
         <v>113</v>
       </c>
       <c r="J193" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K193" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L193" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="194">
@@ -6707,7 +6707,7 @@
         <v>97</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C195" s="0">
         <v>1</v>
@@ -6716,7 +6716,7 @@
         <v>105</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F195" s="0" t="s">
         <v>109</v>
@@ -6729,13 +6729,13 @@
         <v>113</v>
       </c>
       <c r="J195" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K195" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L195" s="0" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="196">
@@ -6771,7 +6771,7 @@
         <v>98</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C197" s="0">
         <v>1</v>
@@ -6780,7 +6780,7 @@
         <v>106</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F197" s="0" t="s">
         <v>109</v>
@@ -6793,13 +6793,13 @@
         <v>113</v>
       </c>
       <c r="J197" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K197" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L197" s="0" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="198">
